--- a/stores.xlsx
+++ b/stores.xlsx
@@ -11,7 +11,7 @@
     <sheet name="政策模板" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'注册信息'!$A$1:$Q$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'注册信息'!$A$1:$Q$4</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -669,7 +669,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,6 +698,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1110,8 +1117,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
+  <dimension ref="A1:W5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -1329,7 +1336,7 @@
           <t>gmeubuy2</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>wqeeveqtnqgx@outlook.com</t>
         </is>
@@ -1398,7 +1405,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="135" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>k1h7vwnu</t>
@@ -1459,40 +1466,107 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>https://admin.shopify.com/store/hme1ge-ei/settings/legal?activator=legal-notice</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="n"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:16:10</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>店铺资料失败：找不到店铺地址编辑入口；退货规则已保存；书面政策已发布；当前店铺无 Terms of sale 入口，已跳过该项；未填产品CSV，跳过导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>k1h7xi9s</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>gmeubuy_esshop</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>kdqjkoeqai@outlook.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>xeqkgl1712</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Shp!XOqclvjQEbli</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Joaquina P Sierra</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>C/ Andalucía 42</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Antas</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Almería (AL)</t>
+        </is>
+      </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>04628</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>711 460 488</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>https://admin.shopify.com/store/hme1ge-ei/settings/legal</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>后续设置未完成：店铺资料：Locator.wait_for: Timeout 15000ms exceeded.
-Call log:
-waiting for get_by_text("Store contact details").first to be visible
-；退货规则已保存；书面政策失败：打不开 Terms of sale；未填产品CSV，跳过导入</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-09-22 17:51:43</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>店铺资料：Locator.wait_for: Timeout 15000ms exceeded.
-Call log:
-waiting for get_by_text("Store contact details").first to be visible
-；退货规则已保存；书面政策失败：打不开 Terms of sale；未填产品CSV，跳过导入</t>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>AdsPower 启动环境 k1h7xi9s 失败：SunBrowser 152 is updating, waiting for download.。若提示代理相关，请先在该环境里把代理测通。</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:27:41</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q3"/>
+  <autoFilter ref="A1:Q4"/>
   <dataValidations count="1">
-    <dataValidation sqref="N2:N200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N3 N4 N5:N200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待处理,成功,失败"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1500,6 +1574,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" display="xbuchysygrfpzoi@outlook.com" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" display="wqeeveqtnqgx@outlook.com" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" tooltip="mailto:uwdcguztasuvgs@outlook.com" display="uwdcguztasuvgs@outlook.com" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" display="kdqjkoeqai@outlook.com" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
